--- a/APP.xlsx
+++ b/APP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CF562-452D-400F-B4C5-7BADF1FE299D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B94714-98A7-4C8D-9B1E-7DF40B3D1A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56990" yWindow="4350" windowWidth="18720" windowHeight="17090" xr2:uid="{9D3513DD-3418-4219-8827-A91F6C35E82B}"/>
+    <workbookView xWindow="15760" yWindow="650" windowWidth="22070" windowHeight="15460" activeTab="1" xr2:uid="{9D3513DD-3418-4219-8827-A91F6C35E82B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,38 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={636ED7F0-D535-4D24-970C-F779D782016A}</author>
+    <author>tc={5B4B2F86-A43F-4ABE-B786-15E06723EA2A}</author>
     <author>tc={8776E06D-3F74-4C5D-B909-5F514E8271F4}</author>
     <author>tc={5A58F8D1-7321-4C11-BE33-FD86458168C1}</author>
     <author>tc={752097DE-873B-4560-9FF1-60771E356C8D}</author>
+    <author>tc={B2402297-0375-440D-85FD-152BE469B558}</author>
+    <author>tc={929DEE8D-5D3A-4FD8-BFD5-091C8EF151E0}</author>
+    <author>tc={D5193C2B-86F7-43E5-BFE4-348824A0994B}</author>
+    <author>tc={CFD90A10-95E1-4685-9737-744BC3CDE9F7}</author>
+    <author>tc={E36349A3-74AB-4B42-A703-37C331ADDB42}</author>
+    <author>tc={EE903976-C52D-4088-A73E-B356AF686565}</author>
+    <author>tc={E2A2FECB-85E3-4500-AA7E-EE309E13D936}</author>
+    <author>tc={4733732B-E8EF-4457-A19A-4F0F1DEF3D41}</author>
   </authors>
   <commentList>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{8776E06D-3F74-4C5D-B909-5F514E8271F4}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{636ED7F0-D535-4D24-970C-F779D782016A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 1080m</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="1" shapeId="0" xr:uid="{5B4B2F86-A43F-4ABE-B786-15E06723EA2A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 1198.235m</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="2" shapeId="0" xr:uid="{8776E06D-3F74-4C5D-B909-5F514E8271F4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +80,7 @@
 5/7/25 Godel eps 1.44, BB 1.46</t>
       </text>
     </comment>
-    <comment ref="L5" authorId="1" shapeId="0" xr:uid="{5A58F8D1-7321-4C11-BE33-FD86458168C1}">
+    <comment ref="L5" authorId="3" shapeId="0" xr:uid="{5A58F8D1-7321-4C11-BE33-FD86458168C1}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -63,7 +89,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="S5" authorId="2" shapeId="0" xr:uid="{752097DE-873B-4560-9FF1-60771E356C8D}">
+    <comment ref="X5" authorId="4" shapeId="0" xr:uid="{752097DE-873B-4560-9FF1-60771E356C8D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -71,12 +97,76 @@
     5/7/25 BB, GD consensus 5.63B</t>
       </text>
     </comment>
+    <comment ref="H6" authorId="5" shapeId="0" xr:uid="{B2402297-0375-440D-85FD-152BE469B558}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 283m</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="6" shapeId="0" xr:uid="{929DEE8D-5D3A-4FD8-BFD5-091C8EF151E0}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 269.659m </t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="7" shapeId="0" xr:uid="{D5193C2B-86F7-43E5-BFE4-348824A0994B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 202m</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="8" shapeId="0" xr:uid="{CFD90A10-95E1-4685-9737-744BC3CDE9F7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 206m</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="9" shapeId="0" xr:uid="{E36349A3-74AB-4B42-A703-37C331ADDB42}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 39m</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="10" shapeId="0" xr:uid="{EE903976-C52D-4088-A73E-B356AF686565}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 150m</t>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="11" shapeId="0" xr:uid="{E2A2FECB-85E3-4500-AA7E-EE309E13D936}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 41m</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="12" shapeId="0" xr:uid="{4733732B-E8EF-4457-A19A-4F0F1DEF3D41}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 38m?</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
   <si>
     <t>Price</t>
   </si>
@@ -193,13 +283,64 @@
   </si>
   <si>
     <t>CFFO margin</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Prepaids</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>ONCA</t>
+  </si>
+  <si>
+    <t>L+SE</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>ONCL</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -219,6 +360,12 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -293,16 +440,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>30079</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>35600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>43447</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>30079</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3342</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>35600</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>138044</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -317,8 +464,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6784474" y="43447"/>
-          <a:ext cx="0" cy="5100053"/>
+          <a:off x="8599817" y="0"/>
+          <a:ext cx="0" cy="7354957"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -343,13 +490,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>36909</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>36909</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>120025</xdr:rowOff>
@@ -717,6 +864,12 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H5" dT="2026-01-20T19:19:45.91" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{636ED7F0-D535-4D24-970C-F779D782016A}">
+    <text>Was 1080m</text>
+  </threadedComment>
+  <threadedComment ref="I5" dT="2026-01-20T19:14:18.36" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{5B4B2F86-A43F-4ABE-B786-15E06723EA2A}">
+    <text>Was 1198.235m</text>
+  </threadedComment>
   <threadedComment ref="K5" dT="2025-05-07T17:42:44.05" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{8776E06D-3F74-4C5D-B909-5F514E8271F4}">
     <text>Q424 guidance: 1355-1385
 5/7/25 consensus 1380
@@ -726,8 +879,32 @@
     <text xml:space="preserve">5/7/25 consensus: 1400m, BB 1390m
 </text>
   </threadedComment>
-  <threadedComment ref="S5" dT="2025-05-07T17:47:14.90" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{752097DE-873B-4560-9FF1-60771E356C8D}">
+  <threadedComment ref="X5" dT="2025-05-07T17:47:14.90" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{752097DE-873B-4560-9FF1-60771E356C8D}">
     <text>5/7/25 BB, GD consensus 5.63B</text>
+  </threadedComment>
+  <threadedComment ref="H6" dT="2026-01-20T19:19:51.07" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{B2402297-0375-440D-85FD-152BE469B558}">
+    <text>Was 283m</text>
+  </threadedComment>
+  <threadedComment ref="I6" dT="2026-01-20T19:14:37.14" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{929DEE8D-5D3A-4FD8-BFD5-091C8EF151E0}">
+    <text xml:space="preserve">Was 269.659m </text>
+  </threadedComment>
+  <threadedComment ref="H8" dT="2026-01-20T19:19:57.89" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{D5193C2B-86F7-43E5-BFE4-348824A0994B}">
+    <text>Was 202m</text>
+  </threadedComment>
+  <threadedComment ref="I8" dT="2026-01-20T19:14:46.40" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{CFD90A10-95E1-4685-9737-744BC3CDE9F7}">
+    <text>Was 206m</text>
+  </threadedComment>
+  <threadedComment ref="H9" dT="2026-01-20T19:20:04.24" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{E36349A3-74AB-4B42-A703-37C331ADDB42}">
+    <text>Was 39m</text>
+  </threadedComment>
+  <threadedComment ref="I9" dT="2026-01-20T19:14:53.03" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{EE903976-C52D-4088-A73E-B356AF686565}">
+    <text>Was 150m</text>
+  </threadedComment>
+  <threadedComment ref="H10" dT="2026-01-20T19:20:28.08" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{E2A2FECB-85E3-4500-AA7E-EE309E13D936}">
+    <text>Was 41m</text>
+  </threadedComment>
+  <threadedComment ref="I10" dT="2026-01-20T19:14:59.76" personId="{CDCF3CD3-C500-4AF0-9498-24228DD1F3D6}" id="{4733732B-E8EF-4457-A19A-4F0F1DEF3D41}">
+    <text>Was 38m?</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -742,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>300.52</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="10:12" x14ac:dyDescent="0.25">
@@ -750,11 +927,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="2">
-        <f>298.667774+36.92403</f>
-        <v>335.59180400000002</v>
+        <v>341</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="10:12" x14ac:dyDescent="0.25">
@@ -763,7 +939,7 @@
       </c>
       <c r="K4" s="2">
         <f>+K2*K3</f>
-        <v>100852.04893808</v>
+        <v>191983</v>
       </c>
     </row>
     <row r="5" spans="10:12" x14ac:dyDescent="0.25">
@@ -771,10 +947,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <v>567.596</v>
+        <v>1667</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="10:12" x14ac:dyDescent="0.25">
@@ -782,10 +958,10 @@
         <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>3474.4560000000001</v>
+        <v>3512</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="10:12" x14ac:dyDescent="0.25">
@@ -794,7 +970,7 @@
       </c>
       <c r="K7" s="2">
         <f>+K4-K5+K6</f>
-        <v>103758.90893808</v>
+        <v>193828</v>
       </c>
     </row>
   </sheetData>
@@ -804,25 +980,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D786880E-57D9-4582-ABFA-84647DFD24DC}">
-  <dimension ref="A1:CF30"/>
+  <dimension ref="A1:CK43"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="9.1796875" style="3"/>
-    <col min="20" max="20" width="9.26953125" customWidth="1"/>
-    <col min="24" max="24" width="8.26953125" customWidth="1"/>
-    <col min="28" max="28" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.26953125" customWidth="1"/>
+    <col min="29" max="29" width="8.26953125" customWidth="1"/>
+    <col min="33" max="33" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
@@ -859,26 +1035,39 @@
       <c r="N2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Q2">
+      <c r="O2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="3"/>
+      <c r="V2">
         <v>2023</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>2024</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>2025</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>2026</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>2027</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>2028</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
@@ -900,8 +1089,13 @@
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
-    </row>
-    <row r="4" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
@@ -923,8 +1117,13 @@
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
-    </row>
-    <row r="5" spans="1:22" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:27" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
@@ -944,43 +1143,61 @@
         <v>1058.115</v>
       </c>
       <c r="H5" s="7">
-        <v>1080.1189999999999</v>
+        <v>711.01499999999999</v>
       </c>
       <c r="I5" s="7">
-        <v>1198.2349999999999</v>
+        <v>835.18600000000004</v>
       </c>
       <c r="J5" s="7">
         <v>1372.779</v>
       </c>
       <c r="K5" s="6">
-        <v>1390</v>
+        <v>1484.021</v>
       </c>
       <c r="L5" s="6">
-        <f>+H5*1.3</f>
-        <v>1404.1547</v>
+        <v>1258.7539999999999</v>
       </c>
       <c r="M5" s="6">
-        <f>+I5*1.29</f>
-        <v>1545.7231499999998</v>
+        <v>1405.0450000000001</v>
       </c>
       <c r="N5" s="6">
-        <f>+J5*1.28</f>
-        <v>1757.1571200000001</v>
+        <f>+J3*1.6</f>
+        <v>1599.1792</v>
+      </c>
+      <c r="O5" s="6">
+        <f>1100*1.5</f>
+        <v>1650</v>
+      </c>
+      <c r="P5" s="6">
+        <f>+L5*1.4</f>
+        <v>1762.2555999999997</v>
       </c>
       <c r="Q5" s="6">
+        <f>+M5*1.3</f>
+        <v>1826.5585000000001</v>
+      </c>
+      <c r="R5" s="6">
+        <f>+N5*1.5</f>
+        <v>2398.7687999999998</v>
+      </c>
+      <c r="V5" s="6">
         <f>SUM(C5:F5)</f>
         <v>3283.087</v>
       </c>
-      <c r="R5" s="6">
+      <c r="W5" s="6">
         <f>SUM(G5:J5)</f>
-        <v>4709.2479999999996</v>
-      </c>
-      <c r="S5" s="6">
+        <v>3977.0950000000003</v>
+      </c>
+      <c r="X5" s="6">
         <f>SUM(K5:N5)</f>
-        <v>6097.0349699999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>5746.9992000000002</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>SUM(O5:R5)</f>
+        <v>7637.5828999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
@@ -994,18 +1211,61 @@
       <c r="F6" s="5">
         <v>273.60700000000003</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5">
+        <v>294.14800000000002</v>
+      </c>
       <c r="H6" s="5">
-        <v>282.54700000000003</v>
+        <v>121.759</v>
       </c>
       <c r="I6" s="5">
-        <v>269.65899999999999</v>
+        <v>120.919</v>
       </c>
       <c r="J6" s="5">
         <v>320.452</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="2">
+        <v>271.23200000000003</v>
+      </c>
+      <c r="L6" s="2">
+        <v>155.07599999999999</v>
+      </c>
+      <c r="M6" s="2">
+        <v>174.85499999999999</v>
+      </c>
+      <c r="N6" s="2">
+        <f>+N5-N7</f>
+        <v>191.90150399999993</v>
+      </c>
+      <c r="O6" s="2">
+        <f t="shared" ref="O6:R6" si="0">+O5-O7</f>
+        <v>198</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" si="0"/>
+        <v>211.47067199999992</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="0"/>
+        <v>219.18702000000008</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="0"/>
+        <v>287.85225600000012</v>
+      </c>
+      <c r="W6" s="2">
+        <f>SUM(G6:J6)</f>
+        <v>857.27800000000002</v>
+      </c>
+      <c r="X6" s="2">
+        <f>SUM(K6:N6)</f>
+        <v>793.06450399999994</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>SUM(O6:R6)</f>
+        <v>916.50994800000012</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1022,21 +1282,68 @@
         <f>+F5-F6</f>
         <v>679.654</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="2">
+        <f>+G5-G6</f>
+        <v>763.96699999999998</v>
+      </c>
       <c r="H7" s="5">
         <f>+H5-H6</f>
-        <v>797.57199999999989</v>
+        <v>589.25599999999997</v>
       </c>
       <c r="I7" s="5">
         <f>+I5-I6</f>
-        <v>928.57599999999991</v>
+        <v>714.26700000000005</v>
       </c>
       <c r="J7" s="5">
         <f>+J5-J6</f>
         <v>1052.327</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="2">
+        <f>+K5-K6</f>
+        <v>1212.789</v>
+      </c>
+      <c r="L7" s="2">
+        <f>+L5-L6</f>
+        <v>1103.6779999999999</v>
+      </c>
+      <c r="M7" s="2">
+        <f>+M5-M6</f>
+        <v>1230.19</v>
+      </c>
+      <c r="N7" s="2">
+        <f>+N5*0.88</f>
+        <v>1407.2776960000001</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:R7" si="1">+O5*0.88</f>
+        <v>1452</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="1"/>
+        <v>1550.7849279999998</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" si="1"/>
+        <v>1607.37148</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" si="1"/>
+        <v>2110.9165439999997</v>
+      </c>
+      <c r="W7" s="2">
+        <f>+W5-W6</f>
+        <v>3119.817</v>
+      </c>
+      <c r="X7" s="2">
+        <f>+X5-X6</f>
+        <v>4953.9346960000003</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>+Y5-Y6</f>
+        <v>6721.0729519999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1050,18 +1357,61 @@
       <c r="F8" s="5">
         <v>222.96299999999999</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5">
+        <v>226.68700000000001</v>
+      </c>
       <c r="H8" s="5">
-        <v>202.107</v>
+        <v>66.965000000000003</v>
       </c>
       <c r="I8" s="5">
-        <v>205.75299999999999</v>
+        <v>62.984000000000002</v>
       </c>
       <c r="J8" s="5">
         <v>214.66200000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K8" s="2">
+        <v>182.95599999999999</v>
+      </c>
+      <c r="L8" s="2">
+        <v>46.917000000000002</v>
+      </c>
+      <c r="M8" s="2">
+        <v>48.575000000000003</v>
+      </c>
+      <c r="N8" s="2">
+        <f>+M8</f>
+        <v>48.575000000000003</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" ref="O8:R8" si="2">+N8</f>
+        <v>48.575000000000003</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="2"/>
+        <v>48.575000000000003</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="2"/>
+        <v>48.575000000000003</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="2"/>
+        <v>48.575000000000003</v>
+      </c>
+      <c r="W8" s="2">
+        <f t="shared" ref="W8:W10" si="3">SUM(G8:J8)</f>
+        <v>571.298</v>
+      </c>
+      <c r="X8" s="2">
+        <f t="shared" ref="X8:X10" si="4">SUM(K8:N8)</f>
+        <v>327.02299999999997</v>
+      </c>
+      <c r="Y8" s="2">
+        <f t="shared" ref="Y8:Y10" si="5">SUM(O8:R8)</f>
+        <v>194.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
@@ -1075,18 +1425,61 @@
       <c r="F9" s="5">
         <v>150.82300000000001</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5">
+        <v>155.32300000000001</v>
+      </c>
       <c r="H9" s="5">
-        <v>163.89599999999999</v>
+        <v>99.123000000000005</v>
       </c>
       <c r="I9" s="5">
-        <v>149.99</v>
+        <v>80.775999999999996</v>
       </c>
       <c r="J9" s="5">
         <v>169.48</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="2">
+        <v>122.91800000000001</v>
+      </c>
+      <c r="L9" s="2">
+        <v>44.031999999999996</v>
+      </c>
+      <c r="M9" s="2">
+        <v>43.851999999999997</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" ref="N9:R9" si="6">+M9</f>
+        <v>43.851999999999997</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="6"/>
+        <v>43.851999999999997</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="6"/>
+        <v>43.851999999999997</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="6"/>
+        <v>43.851999999999997</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="6"/>
+        <v>43.851999999999997</v>
+      </c>
+      <c r="W9" s="2">
+        <f t="shared" si="3"/>
+        <v>504.702</v>
+      </c>
+      <c r="X9" s="2">
+        <f t="shared" si="4"/>
+        <v>254.654</v>
+      </c>
+      <c r="Y9" s="2">
+        <f t="shared" si="5"/>
+        <v>175.40799999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1100,18 +1493,61 @@
       <c r="F10" s="5">
         <v>36.353999999999999</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5">
+        <v>42.398000000000003</v>
+      </c>
       <c r="H10" s="5">
-        <v>40.582999999999998</v>
+        <v>38.746000000000002</v>
       </c>
       <c r="I10" s="5">
-        <v>37.899000000000001</v>
+        <v>36.207999999999998</v>
       </c>
       <c r="J10" s="5">
         <v>60.204999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="2">
+        <v>54.500999999999998</v>
+      </c>
+      <c r="L10" s="2">
+        <v>55.046999999999997</v>
+      </c>
+      <c r="M10" s="2">
+        <v>58.756</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" ref="N10:R10" si="7">+M10</f>
+        <v>58.756</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" si="7"/>
+        <v>58.756</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="7"/>
+        <v>58.756</v>
+      </c>
+      <c r="Q10" s="2">
+        <f t="shared" si="7"/>
+        <v>58.756</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="7"/>
+        <v>58.756</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" si="3"/>
+        <v>177.55700000000002</v>
+      </c>
+      <c r="X10" s="2">
+        <f t="shared" si="4"/>
+        <v>227.06</v>
+      </c>
+      <c r="Y10" s="2">
+        <f t="shared" si="5"/>
+        <v>235.024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1128,21 +1564,72 @@
         <f>+F10+F9+F8</f>
         <v>410.14</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" ref="G11" si="8">+G10+G9+G8</f>
+        <v>424.40800000000002</v>
+      </c>
       <c r="H11" s="5">
         <f>+H10+H9+H8</f>
-        <v>406.58600000000001</v>
+        <v>204.834</v>
       </c>
       <c r="I11" s="5">
         <f>+I10+I9+I8</f>
-        <v>393.642</v>
+        <v>179.96799999999999</v>
       </c>
       <c r="J11" s="5">
         <f>+J10+J9+J8</f>
         <v>444.34699999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="5">
+        <f t="shared" ref="K11:N11" si="9">+K10+K9+K8</f>
+        <v>360.375</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="9"/>
+        <v>145.99599999999998</v>
+      </c>
+      <c r="M11" s="5">
+        <f t="shared" si="9"/>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="9"/>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="O11" s="5">
+        <f t="shared" ref="O11" si="10">+O10+O9+O8</f>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="P11" s="5">
+        <f t="shared" ref="P11" si="11">+P10+P9+P8</f>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" ref="Q11" si="12">+Q10+Q9+Q8</f>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" ref="R11" si="13">+R10+R9+R8</f>
+        <v>151.18299999999999</v>
+      </c>
+      <c r="V11" s="5">
+        <f t="shared" ref="V11" si="14">+V10+V9+V8</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" ref="W11" si="15">+W10+W9+W8</f>
+        <v>1253.557</v>
+      </c>
+      <c r="X11" s="5">
+        <f t="shared" ref="X11" si="16">+X10+X9+X8</f>
+        <v>808.73699999999997</v>
+      </c>
+      <c r="Y11" s="5">
+        <f t="shared" ref="Y11" si="17">+Y10+Y9+Y8</f>
+        <v>604.73199999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1159,21 +1646,72 @@
         <f>+F7-F11</f>
         <v>269.51400000000001</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" ref="G12" si="18">+G7-G11</f>
+        <v>339.55899999999997</v>
+      </c>
       <c r="H12" s="5">
         <f>+H7-H11</f>
-        <v>390.98599999999988</v>
+        <v>384.42199999999997</v>
       </c>
       <c r="I12" s="5">
         <f>+I7-I11</f>
-        <v>534.93399999999997</v>
+        <v>534.29900000000009</v>
       </c>
       <c r="J12" s="5">
         <f>+J7-J11</f>
         <v>607.98</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K12" s="5">
+        <f t="shared" ref="K12:N12" si="19">+K7-K11</f>
+        <v>852.41399999999999</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="19"/>
+        <v>957.6819999999999</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="19"/>
+        <v>1079.0070000000001</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="19"/>
+        <v>1256.0946960000001</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" ref="O12" si="20">+O7-O11</f>
+        <v>1300.817</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" ref="P12" si="21">+P7-P11</f>
+        <v>1399.6019279999998</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" ref="Q12" si="22">+Q7-Q11</f>
+        <v>1456.18848</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" ref="R12" si="23">+R7-R11</f>
+        <v>1959.7335439999997</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" ref="V12" si="24">+V7-V11</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" ref="W12" si="25">+W7-W11</f>
+        <v>1866.26</v>
+      </c>
+      <c r="X12" s="5">
+        <f t="shared" ref="X12" si="26">+X7-X11</f>
+        <v>4145.1976960000002</v>
+      </c>
+      <c r="Y12" s="5">
+        <f t="shared" ref="Y12" si="27">+Y7-Y11</f>
+        <v>6116.3409519999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
@@ -1188,21 +1726,42 @@
       <c r="F13" s="5">
         <v>-71.584000000000003</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="5">
+        <v>-74.182000000000002</v>
+      </c>
       <c r="H13" s="5">
-        <f>-74.666+8.947</f>
-        <v>-65.718999999999994</v>
+        <v>-74.418000000000006</v>
       </c>
       <c r="I13" s="5">
-        <f>-75.213+7.948</f>
-        <v>-67.264999999999986</v>
+        <v>-74.936999999999998</v>
       </c>
       <c r="J13" s="5">
         <f>-94.199+1.343</f>
         <v>-92.855999999999995</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="2">
+        <v>-52.887999999999998</v>
+      </c>
+      <c r="L13" s="2">
+        <v>-51.408999999999999</v>
+      </c>
+      <c r="M13" s="2">
+        <v>-51.429000000000002</v>
+      </c>
+      <c r="W13" s="2">
+        <f t="shared" ref="W13" si="28">SUM(G13:J13)</f>
+        <v>-316.39300000000003</v>
+      </c>
+      <c r="X13" s="2">
+        <f t="shared" ref="X13:X15" si="29">SUM(K13:N13)</f>
+        <v>-155.726</v>
+      </c>
+      <c r="Y13" s="2">
+        <f t="shared" ref="Y13" si="30">SUM(O13:R13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1219,21 +1778,72 @@
         <f>+F12+F13</f>
         <v>197.93</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5">
+        <f>+G12+G13</f>
+        <v>265.37699999999995</v>
+      </c>
       <c r="H14" s="5">
         <f>+H12+H13</f>
-        <v>325.26699999999988</v>
+        <v>310.00399999999996</v>
       </c>
       <c r="I14" s="5">
         <f>+I12+I13</f>
-        <v>467.66899999999998</v>
+        <v>459.36200000000008</v>
       </c>
       <c r="J14" s="5">
         <f>+J12+J13</f>
         <v>515.12400000000002</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="5">
+        <f>+K12+K13</f>
+        <v>799.52599999999995</v>
+      </c>
+      <c r="L14" s="5">
+        <f>+L12+L13</f>
+        <v>906.27299999999991</v>
+      </c>
+      <c r="M14" s="5">
+        <f>+M12+M13</f>
+        <v>1027.578</v>
+      </c>
+      <c r="N14" s="5">
+        <f>+N12+N13</f>
+        <v>1256.0946960000001</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" ref="O14:R14" si="31">+O12+O13</f>
+        <v>1300.817</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="31"/>
+        <v>1399.6019279999998</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="31"/>
+        <v>1456.18848</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="31"/>
+        <v>1959.7335439999997</v>
+      </c>
+      <c r="V14" s="5">
+        <f t="shared" ref="V14" si="32">+V12+V13</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="5">
+        <f t="shared" ref="W14" si="33">+W12+W13</f>
+        <v>1549.867</v>
+      </c>
+      <c r="X14" s="5">
+        <f t="shared" ref="X14" si="34">+X12+X13</f>
+        <v>3989.4716960000001</v>
+      </c>
+      <c r="Y14" s="5">
+        <f t="shared" ref="Y14" si="35">+Y12+Y13</f>
+        <v>6116.3409519999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
@@ -1247,18 +1857,61 @@
       <c r="F15" s="5">
         <v>6.6630000000000003</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5">
+        <v>31.762</v>
+      </c>
       <c r="H15" s="5">
-        <v>15.298</v>
+        <v>16.893999999999998</v>
       </c>
       <c r="I15" s="5">
-        <v>33.249000000000002</v>
+        <v>34.655999999999999</v>
       </c>
       <c r="J15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="2">
+        <v>41.975000000000001</v>
+      </c>
+      <c r="L15" s="2">
+        <v>112.148</v>
+      </c>
+      <c r="M15" s="2">
+        <v>185.40100000000001</v>
+      </c>
+      <c r="N15" s="2">
+        <f>+N14*0.2</f>
+        <v>251.21893920000002</v>
+      </c>
+      <c r="O15" s="2">
+        <f t="shared" ref="O15:R15" si="36">+O14*0.2</f>
+        <v>260.16340000000002</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="36"/>
+        <v>279.92038559999997</v>
+      </c>
+      <c r="Q15" s="2">
+        <f t="shared" si="36"/>
+        <v>291.23769600000003</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" si="36"/>
+        <v>391.94670879999995</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" ref="W15" si="37">SUM(G15:J15)</f>
+        <v>83.311999999999998</v>
+      </c>
+      <c r="X15" s="2">
+        <f t="shared" si="29"/>
+        <v>590.74293920000002</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" ref="Y15" si="38">SUM(O15:R15)</f>
+        <v>1223.2681904000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1275,21 +1928,72 @@
         <f>+F14-F15</f>
         <v>191.267</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="5">
+        <f>+G14-G15</f>
+        <v>233.61499999999995</v>
+      </c>
       <c r="H16" s="5">
         <f>+H14-H15</f>
-        <v>309.96899999999988</v>
+        <v>293.10999999999996</v>
       </c>
       <c r="I16" s="5">
         <f>+I14-I15</f>
-        <v>434.41999999999996</v>
+        <v>424.70600000000007</v>
       </c>
       <c r="J16" s="5">
         <f>+J14-J15</f>
         <v>515.12400000000002</v>
       </c>
-    </row>
-    <row r="17" spans="2:84" x14ac:dyDescent="0.25">
+      <c r="K16" s="5">
+        <f>+K14-K15</f>
+        <v>757.55099999999993</v>
+      </c>
+      <c r="L16" s="5">
+        <f>+L14-L15</f>
+        <v>794.12499999999989</v>
+      </c>
+      <c r="M16" s="5">
+        <f>+M14-M15</f>
+        <v>842.17699999999991</v>
+      </c>
+      <c r="N16" s="5">
+        <f>+N14-N15</f>
+        <v>1004.8757568000001</v>
+      </c>
+      <c r="O16" s="5">
+        <f t="shared" ref="O16:R16" si="39">+O14-O15</f>
+        <v>1040.6536000000001</v>
+      </c>
+      <c r="P16" s="5">
+        <f t="shared" si="39"/>
+        <v>1119.6815423999999</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" si="39"/>
+        <v>1164.9507840000001</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" si="39"/>
+        <v>1567.7868351999998</v>
+      </c>
+      <c r="V16" s="5">
+        <f t="shared" ref="V16" si="40">+V14-V15</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" ref="W16" si="41">+W14-W15</f>
+        <v>1466.5550000000001</v>
+      </c>
+      <c r="X16" s="5">
+        <f t="shared" ref="X16" si="42">+X14-X15</f>
+        <v>3398.7287568000002</v>
+      </c>
+      <c r="Y16" s="5">
+        <f t="shared" ref="Y16" si="43">+Y14-Y15</f>
+        <v>4893.0727615999995</v>
+      </c>
+    </row>
+    <row r="17" spans="2:89" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
@@ -1307,18 +2011,62 @@
       </c>
       <c r="H17" s="4">
         <f>+H16/H18</f>
-        <v>0.89080715518778286</v>
+        <v>0.84235676876426713</v>
       </c>
       <c r="I17" s="4">
         <f>+I16/I18</f>
-        <v>1.2475250840573942</v>
+        <v>1.2196309857132603</v>
       </c>
       <c r="J17" s="4">
         <f>+J16/J18</f>
         <v>1.4869761506719363</v>
       </c>
-    </row>
-    <row r="18" spans="2:84" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K17" s="4">
+        <f t="shared" ref="K17:N17" si="44">+K16/K18</f>
+        <v>2.1867749705268555</v>
+      </c>
+      <c r="L17" s="4">
+        <f t="shared" si="44"/>
+        <v>2.3206835746506722</v>
+      </c>
+      <c r="M17" s="4">
+        <f t="shared" si="44"/>
+        <v>2.4699155947374285</v>
+      </c>
+      <c r="N17" s="4">
+        <f t="shared" si="44"/>
+        <v>2.9470744303084695</v>
+      </c>
+      <c r="O17" s="4">
+        <f t="shared" ref="O17" si="45">+O16/O18</f>
+        <v>3.0520027920017365</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" ref="P17" si="46">+P16/P18</f>
+        <v>3.2837739604779248</v>
+      </c>
+      <c r="Q17" s="4">
+        <f t="shared" ref="Q17" si="47">+Q16/Q18</f>
+        <v>3.4165384574776967</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" ref="R17" si="48">+R16/R18</f>
+        <v>4.5979659305401581</v>
+      </c>
+      <c r="W17" s="4">
+        <f t="shared" ref="W17:Y17" si="49">+W16/W18</f>
+        <v>4.2198445571152643</v>
+      </c>
+      <c r="X17" s="4">
+        <f t="shared" si="49"/>
+        <v>9.9191956023322021</v>
+      </c>
+      <c r="Y17" s="4">
+        <f t="shared" si="49"/>
+        <v>14.350281140497515</v>
+      </c>
+    </row>
+    <row r="18" spans="2:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
@@ -1337,13 +2085,55 @@
         <v>347.964201</v>
       </c>
       <c r="I18" s="5">
-        <v>348.22546299999999</v>
+        <v>348.22500000000002</v>
       </c>
       <c r="J18" s="5">
         <v>346.42384800000002</v>
       </c>
-    </row>
-    <row r="20" spans="2:84" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="K18" s="2">
+        <f>+J18</f>
+        <v>346.42384800000002</v>
+      </c>
+      <c r="L18" s="2">
+        <v>342.194433</v>
+      </c>
+      <c r="M18" s="2">
+        <v>340.97399999999999</v>
+      </c>
+      <c r="N18" s="2">
+        <f>+M18</f>
+        <v>340.97399999999999</v>
+      </c>
+      <c r="O18" s="2">
+        <f t="shared" ref="O18:R18" si="50">+N18</f>
+        <v>340.97399999999999</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" si="50"/>
+        <v>340.97399999999999</v>
+      </c>
+      <c r="Q18" s="2">
+        <f t="shared" si="50"/>
+        <v>340.97399999999999</v>
+      </c>
+      <c r="R18" s="2">
+        <f t="shared" si="50"/>
+        <v>340.97399999999999</v>
+      </c>
+      <c r="W18" s="2">
+        <f>AVERAGE(G18:J18)</f>
+        <v>347.53768300000002</v>
+      </c>
+      <c r="X18" s="2">
+        <f>AVERAGE(K18:N18)</f>
+        <v>342.64157024999997</v>
+      </c>
+      <c r="Y18" s="2">
+        <f>AVERAGE(O18:R18)</f>
+        <v>340.97399999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:89" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>32</v>
       </c>
@@ -1357,11 +2147,11 @@
       </c>
       <c r="H20" s="10">
         <f>+H5/D5-1</f>
-        <v>0.43984190144834789</v>
+        <v>-5.2188518525924321E-2</v>
       </c>
       <c r="I20" s="10">
         <f>+I5/E5-1</f>
-        <v>0.38643526917950233</v>
+        <v>-3.3635867150473842E-2</v>
       </c>
       <c r="J20" s="10">
         <f>+J5/F5-1</f>
@@ -1369,30 +2159,84 @@
       </c>
       <c r="K20" s="10">
         <f>+K5/G5-1</f>
-        <v>0.31365683314195536</v>
+        <v>0.40251390444327884</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" ref="L20:N20" si="0">+L5/H5-1</f>
+        <f t="shared" ref="L20:M20" si="51">+L5/H5-1</f>
+        <v>0.77036208800095629</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="51"/>
+        <v>0.68231387978246771</v>
+      </c>
+      <c r="N20" s="10">
+        <f>+N5/J3-1</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O20" s="10">
+        <f>+O5/K5-1</f>
+        <v>0.1118441046319425</v>
+      </c>
+      <c r="P20" s="10">
+        <f>+P5/L5-1</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="Q20" s="10">
+        <f>+Q5/M5-1</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="M20" s="10">
-        <f t="shared" si="0"/>
-        <v>0.29000000000000004</v>
-      </c>
-      <c r="N20" s="10">
-        <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="R20" s="12">
-        <f>+R5/Q5-1</f>
-        <v>0.43439634709649777</v>
-      </c>
-      <c r="S20" s="12">
-        <f>+S5/R5-1</f>
-        <v>0.29469396600051656</v>
-      </c>
-    </row>
-    <row r="23" spans="2:84" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R20" s="10">
+        <f>+R5/N5-1</f>
+        <v>0.49999999999999978</v>
+      </c>
+      <c r="S20" s="10"/>
+      <c r="W20" s="12">
+        <f>+W5/V5-1</f>
+        <v>0.21138885445314126</v>
+      </c>
+      <c r="X20" s="12">
+        <f>+X5/W5-1</f>
+        <v>0.44502437080331236</v>
+      </c>
+      <c r="Y20" s="12">
+        <f>+Y5/X5-1</f>
+        <v>0.32896884690709527</v>
+      </c>
+    </row>
+    <row r="21" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="13">
+        <f>+L7/L5</f>
+        <v>0.87680198037106538</v>
+      </c>
+      <c r="M21" s="13">
+        <f>+M7/M5</f>
+        <v>0.87555202858271441</v>
+      </c>
+      <c r="N21" s="13">
+        <f t="shared" ref="N21:R21" si="52">+N7/N5</f>
+        <v>0.88</v>
+      </c>
+      <c r="O21" s="13">
+        <f t="shared" si="52"/>
+        <v>0.88</v>
+      </c>
+      <c r="P21" s="13">
+        <f t="shared" si="52"/>
+        <v>0.88</v>
+      </c>
+      <c r="Q21" s="13">
+        <f t="shared" si="52"/>
+        <v>0.88</v>
+      </c>
+      <c r="R21" s="13">
+        <f t="shared" si="52"/>
+        <v>0.87999999999999989</v>
+      </c>
+    </row>
+    <row r="23" spans="2:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
@@ -1426,280 +2270,288 @@
         <f>2099.011-I23-H23-G23</f>
         <v>701.00299999999993</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="L23" s="2">
+        <f>378.884-K23</f>
+        <v>378.88400000000001</v>
+      </c>
+      <c r="M23" s="2">
+        <f>2657.36-L23-K23</f>
+        <v>2278.4760000000001</v>
+      </c>
+      <c r="V23" s="2">
         <f>SUM(C23:F23)</f>
         <v>1061.51</v>
       </c>
-      <c r="R23" s="2">
+      <c r="W23" s="2">
         <f>SUM(G23:J23)</f>
         <v>2099.011</v>
       </c>
-      <c r="S23" s="2">
-        <f>+S5*S26</f>
-        <v>3048.5174849999999</v>
-      </c>
-      <c r="T23" s="2">
-        <f>+S23*1.2</f>
-        <v>3658.2209819999998</v>
-      </c>
-      <c r="U23" s="2">
-        <f t="shared" ref="U23:CF23" si="1">+T23*1.2</f>
-        <v>4389.8651783999994</v>
-      </c>
-      <c r="V23" s="2">
-        <f t="shared" si="1"/>
-        <v>5267.8382140799995</v>
-      </c>
-      <c r="W23" s="2">
-        <f t="shared" si="1"/>
-        <v>6321.405856895999</v>
-      </c>
       <c r="X23" s="2">
-        <f t="shared" si="1"/>
-        <v>7585.6870282751988</v>
+        <f>+X5*X26</f>
+        <v>2873.4996000000001</v>
       </c>
       <c r="Y23" s="2">
-        <f t="shared" si="1"/>
-        <v>9102.8244339302382</v>
+        <f>+X23*1.2</f>
+        <v>3448.1995200000001</v>
       </c>
       <c r="Z23" s="2">
-        <f t="shared" si="1"/>
-        <v>10923.389320716286</v>
+        <f t="shared" ref="Z23:CK23" si="53">+Y23*1.2</f>
+        <v>4137.8394239999998</v>
       </c>
       <c r="AA23" s="2">
-        <f t="shared" si="1"/>
-        <v>13108.067184859543</v>
+        <f t="shared" si="53"/>
+        <v>4965.4073087999996</v>
       </c>
       <c r="AB23" s="2">
-        <f t="shared" si="1"/>
-        <v>15729.68062183145</v>
+        <f t="shared" si="53"/>
+        <v>5958.4887705599995</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="1"/>
-        <v>18875.616746197738</v>
+        <f t="shared" si="53"/>
+        <v>7150.186524671999</v>
       </c>
       <c r="AD23" s="2">
-        <f t="shared" si="1"/>
-        <v>22650.740095437286</v>
+        <f t="shared" si="53"/>
+        <v>8580.2238296063988</v>
       </c>
       <c r="AE23" s="2">
-        <f t="shared" si="1"/>
-        <v>27180.888114524743</v>
+        <f t="shared" si="53"/>
+        <v>10296.268595527677</v>
       </c>
       <c r="AF23" s="2">
-        <f t="shared" si="1"/>
-        <v>32617.06573742969</v>
+        <f t="shared" si="53"/>
+        <v>12355.522314633212</v>
       </c>
       <c r="AG23" s="2">
-        <f t="shared" si="1"/>
-        <v>39140.478884915625</v>
+        <f t="shared" si="53"/>
+        <v>14826.626777559854</v>
       </c>
       <c r="AH23" s="2">
-        <f t="shared" si="1"/>
-        <v>46968.574661898747</v>
+        <f t="shared" si="53"/>
+        <v>17791.952133071823</v>
       </c>
       <c r="AI23" s="2">
-        <f t="shared" si="1"/>
-        <v>56362.289594278496</v>
+        <f t="shared" si="53"/>
+        <v>21350.342559686189</v>
       </c>
       <c r="AJ23" s="2">
-        <f t="shared" si="1"/>
-        <v>67634.747513134193</v>
+        <f t="shared" si="53"/>
+        <v>25620.411071623425</v>
       </c>
       <c r="AK23" s="2">
-        <f t="shared" si="1"/>
-        <v>81161.697015761034</v>
+        <f t="shared" si="53"/>
+        <v>30744.493285948109</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="1"/>
-        <v>97394.036418913238</v>
+        <f t="shared" si="53"/>
+        <v>36893.391943137729</v>
       </c>
       <c r="AM23" s="2">
-        <f t="shared" si="1"/>
-        <v>116872.84370269589</v>
+        <f t="shared" si="53"/>
+        <v>44272.070331765273</v>
       </c>
       <c r="AN23" s="2">
-        <f t="shared" si="1"/>
-        <v>140247.41244323505</v>
+        <f t="shared" si="53"/>
+        <v>53126.484398118329</v>
       </c>
       <c r="AO23" s="2">
-        <f t="shared" si="1"/>
-        <v>168296.89493188207</v>
+        <f t="shared" si="53"/>
+        <v>63751.781277741989</v>
       </c>
       <c r="AP23" s="2">
-        <f t="shared" si="1"/>
-        <v>201956.27391825846</v>
+        <f t="shared" si="53"/>
+        <v>76502.137533290384</v>
       </c>
       <c r="AQ23" s="2">
-        <f t="shared" si="1"/>
-        <v>242347.52870191014</v>
+        <f t="shared" si="53"/>
+        <v>91802.565039948458</v>
       </c>
       <c r="AR23" s="2">
-        <f t="shared" si="1"/>
-        <v>290817.03444229218</v>
+        <f t="shared" si="53"/>
+        <v>110163.07804793815</v>
       </c>
       <c r="AS23" s="2">
-        <f t="shared" si="1"/>
-        <v>348980.44133075059</v>
+        <f t="shared" si="53"/>
+        <v>132195.69365752579</v>
       </c>
       <c r="AT23" s="2">
-        <f t="shared" si="1"/>
-        <v>418776.52959690068</v>
+        <f t="shared" si="53"/>
+        <v>158634.83238903093</v>
       </c>
       <c r="AU23" s="2">
-        <f t="shared" si="1"/>
-        <v>502531.83551628079</v>
+        <f t="shared" si="53"/>
+        <v>190361.79886683711</v>
       </c>
       <c r="AV23" s="2">
-        <f t="shared" si="1"/>
-        <v>603038.2026195369</v>
+        <f t="shared" si="53"/>
+        <v>228434.15864020452</v>
       </c>
       <c r="AW23" s="2">
-        <f t="shared" si="1"/>
-        <v>723645.84314344428</v>
+        <f t="shared" si="53"/>
+        <v>274120.9903682454</v>
       </c>
       <c r="AX23" s="2">
-        <f t="shared" si="1"/>
-        <v>868375.01177213306</v>
+        <f t="shared" si="53"/>
+        <v>328945.18844189448</v>
       </c>
       <c r="AY23" s="2">
-        <f t="shared" si="1"/>
-        <v>1042050.0141265596</v>
+        <f t="shared" si="53"/>
+        <v>394734.22613027337</v>
       </c>
       <c r="AZ23" s="2">
-        <f t="shared" si="1"/>
-        <v>1250460.0169518716</v>
+        <f t="shared" si="53"/>
+        <v>473681.07135632803</v>
       </c>
       <c r="BA23" s="2">
-        <f t="shared" si="1"/>
-        <v>1500552.0203422459</v>
+        <f t="shared" si="53"/>
+        <v>568417.28562759364</v>
       </c>
       <c r="BB23" s="2">
-        <f t="shared" si="1"/>
-        <v>1800662.424410695</v>
+        <f t="shared" si="53"/>
+        <v>682100.74275311234</v>
       </c>
       <c r="BC23" s="2">
-        <f t="shared" si="1"/>
-        <v>2160794.9092928339</v>
+        <f t="shared" si="53"/>
+        <v>818520.89130373474</v>
       </c>
       <c r="BD23" s="2">
-        <f t="shared" si="1"/>
-        <v>2592953.8911514007</v>
+        <f t="shared" si="53"/>
+        <v>982225.06956448162</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="1"/>
-        <v>3111544.6693816809</v>
+        <f t="shared" si="53"/>
+        <v>1178670.0834773779</v>
       </c>
       <c r="BF23" s="2">
-        <f t="shared" si="1"/>
-        <v>3733853.603258017</v>
+        <f t="shared" si="53"/>
+        <v>1414404.1001728533</v>
       </c>
       <c r="BG23" s="2">
-        <f t="shared" si="1"/>
-        <v>4480624.3239096198</v>
+        <f t="shared" si="53"/>
+        <v>1697284.9202074239</v>
       </c>
       <c r="BH23" s="2">
-        <f t="shared" si="1"/>
-        <v>5376749.1886915434</v>
+        <f t="shared" si="53"/>
+        <v>2036741.9042489086</v>
       </c>
       <c r="BI23" s="2">
-        <f t="shared" si="1"/>
-        <v>6452099.0264298515</v>
+        <f t="shared" si="53"/>
+        <v>2444090.2850986901</v>
       </c>
       <c r="BJ23" s="2">
-        <f t="shared" si="1"/>
-        <v>7742518.8317158213</v>
+        <f t="shared" si="53"/>
+        <v>2932908.3421184281</v>
       </c>
       <c r="BK23" s="2">
-        <f t="shared" si="1"/>
-        <v>9291022.5980589855</v>
+        <f t="shared" si="53"/>
+        <v>3519490.0105421138</v>
       </c>
       <c r="BL23" s="2">
-        <f t="shared" si="1"/>
-        <v>11149227.117670782</v>
+        <f t="shared" si="53"/>
+        <v>4223388.0126505364</v>
       </c>
       <c r="BM23" s="2">
-        <f t="shared" si="1"/>
-        <v>13379072.541204939</v>
+        <f t="shared" si="53"/>
+        <v>5068065.6151806433</v>
       </c>
       <c r="BN23" s="2">
-        <f t="shared" si="1"/>
-        <v>16054887.049445925</v>
+        <f t="shared" si="53"/>
+        <v>6081678.7382167717</v>
       </c>
       <c r="BO23" s="2">
-        <f t="shared" si="1"/>
-        <v>19265864.459335111</v>
+        <f t="shared" si="53"/>
+        <v>7298014.4858601261</v>
       </c>
       <c r="BP23" s="2">
-        <f t="shared" si="1"/>
-        <v>23119037.351202134</v>
+        <f t="shared" si="53"/>
+        <v>8757617.3830321506</v>
       </c>
       <c r="BQ23" s="2">
-        <f t="shared" si="1"/>
-        <v>27742844.821442559</v>
+        <f t="shared" si="53"/>
+        <v>10509140.859638581</v>
       </c>
       <c r="BR23" s="2">
-        <f t="shared" si="1"/>
-        <v>33291413.78573107</v>
+        <f t="shared" si="53"/>
+        <v>12610969.031566298</v>
       </c>
       <c r="BS23" s="2">
-        <f t="shared" si="1"/>
-        <v>39949696.542877279</v>
+        <f t="shared" si="53"/>
+        <v>15133162.837879557</v>
       </c>
       <c r="BT23" s="2">
-        <f t="shared" si="1"/>
-        <v>47939635.851452731</v>
+        <f t="shared" si="53"/>
+        <v>18159795.405455466</v>
       </c>
       <c r="BU23" s="2">
-        <f t="shared" si="1"/>
-        <v>57527563.021743275</v>
+        <f t="shared" si="53"/>
+        <v>21791754.486546557</v>
       </c>
       <c r="BV23" s="2">
-        <f t="shared" si="1"/>
-        <v>69033075.626091927</v>
+        <f t="shared" si="53"/>
+        <v>26150105.383855868</v>
       </c>
       <c r="BW23" s="2">
-        <f t="shared" si="1"/>
-        <v>82839690.751310304</v>
+        <f t="shared" si="53"/>
+        <v>31380126.460627042</v>
       </c>
       <c r="BX23" s="2">
-        <f t="shared" si="1"/>
-        <v>99407628.901572362</v>
+        <f t="shared" si="53"/>
+        <v>37656151.752752446</v>
       </c>
       <c r="BY23" s="2">
-        <f t="shared" si="1"/>
-        <v>119289154.68188684</v>
+        <f t="shared" si="53"/>
+        <v>45187382.103302933</v>
       </c>
       <c r="BZ23" s="2">
-        <f t="shared" si="1"/>
-        <v>143146985.6182642</v>
+        <f t="shared" si="53"/>
+        <v>54224858.523963518</v>
       </c>
       <c r="CA23" s="2">
-        <f t="shared" si="1"/>
-        <v>171776382.74191704</v>
+        <f t="shared" si="53"/>
+        <v>65069830.228756219</v>
       </c>
       <c r="CB23" s="2">
-        <f t="shared" si="1"/>
-        <v>206131659.29030046</v>
+        <f t="shared" si="53"/>
+        <v>78083796.274507463</v>
       </c>
       <c r="CC23" s="2">
-        <f t="shared" si="1"/>
-        <v>247357991.14836055</v>
+        <f t="shared" si="53"/>
+        <v>93700555.529408947</v>
       </c>
       <c r="CD23" s="2">
-        <f t="shared" si="1"/>
-        <v>296829589.37803262</v>
+        <f t="shared" si="53"/>
+        <v>112440666.63529073</v>
       </c>
       <c r="CE23" s="2">
-        <f t="shared" si="1"/>
-        <v>356195507.25363916</v>
+        <f t="shared" si="53"/>
+        <v>134928799.96234888</v>
       </c>
       <c r="CF23" s="2">
-        <f t="shared" si="1"/>
-        <v>427434608.70436698</v>
-      </c>
-    </row>
-    <row r="24" spans="2:84" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="53"/>
+        <v>161914559.95481864</v>
+      </c>
+      <c r="CG23" s="2">
+        <f t="shared" si="53"/>
+        <v>194297471.94578236</v>
+      </c>
+      <c r="CH23" s="2">
+        <f t="shared" si="53"/>
+        <v>233156966.33493882</v>
+      </c>
+      <c r="CI23" s="2">
+        <f t="shared" si="53"/>
+        <v>279788359.60192657</v>
+      </c>
+      <c r="CJ23" s="2">
+        <f t="shared" si="53"/>
+        <v>335746031.52231187</v>
+      </c>
+      <c r="CK23" s="2">
+        <f t="shared" si="53"/>
+        <v>402895237.82677424</v>
+      </c>
+    </row>
+    <row r="24" spans="2:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1714,8 +2566,16 @@
         <v>-18.289000000000001</v>
       </c>
       <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="2:84" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L24" s="2">
+        <f>-11.807-K24</f>
+        <v>-11.807</v>
+      </c>
+      <c r="M24" s="2">
+        <f>-27.863-L24-K24</f>
+        <v>-16.055999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="2:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
@@ -1733,63 +2593,190 @@
         <f>+J23+J24</f>
         <v>701.00299999999993</v>
       </c>
-    </row>
-    <row r="26" spans="2:84" x14ac:dyDescent="0.25">
+      <c r="K25" s="5">
+        <f t="shared" ref="K25:M25" si="54">+K23+K24</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="54"/>
+        <v>367.077</v>
+      </c>
+      <c r="M25" s="5">
+        <f t="shared" si="54"/>
+        <v>2262.42</v>
+      </c>
+    </row>
+    <row r="26" spans="2:89" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q26" s="13">
-        <f>+Q23/Q5</f>
+      <c r="V26" s="13">
+        <f>+V23/V5</f>
         <v>0.32332679578701384</v>
       </c>
-      <c r="R26" s="13">
-        <f>+R23/R5</f>
-        <v>0.44572105779946186</v>
-      </c>
-      <c r="S26" s="13">
+      <c r="W26" s="13">
+        <f>+W23/W5</f>
+        <v>0.52777492114219038</v>
+      </c>
+      <c r="X26" s="13">
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="2:84" x14ac:dyDescent="0.25">
-      <c r="R28" s="13">
-        <f>+R23/Q23-1</f>
+    <row r="27" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="W27" s="13">
+        <f>+W23/V23-1</f>
         <v>0.97738221966820849</v>
       </c>
-      <c r="S28" s="13">
-        <f>+S23/R23-1</f>
-        <v>0.45235898477902214</v>
-      </c>
-    </row>
-    <row r="29" spans="2:84" x14ac:dyDescent="0.25">
-      <c r="T29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="AB29" s="1">
-        <f>+AB23*20</f>
-        <v>314593.61243662902</v>
-      </c>
-      <c r="AH29" s="1">
-        <f>+AH23*20</f>
-        <v>939371.49323797494</v>
+      <c r="X27" s="13">
+        <f>+X23/W23-1</f>
+        <v>0.368977866242721</v>
+      </c>
+    </row>
+    <row r="28" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+    </row>
+    <row r="29" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="2">
+        <v>1666.8989999999999</v>
+      </c>
+      <c r="Y29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AG29" s="1">
+        <f>+AG23*20</f>
+        <v>296532.53555119707</v>
       </c>
       <c r="AM29" s="1">
         <f>+AM23*20</f>
-        <v>2337456.8740539178</v>
-      </c>
-    </row>
-    <row r="30" spans="2:84" x14ac:dyDescent="0.25">
-      <c r="T30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="AB30" s="1">
-        <f>PV(11%,9,0,-AB29)</f>
-        <v>122982.43603816564</v>
-      </c>
-      <c r="AH30" s="1">
-        <f>PV(11%,15,0,-AH29)</f>
-        <v>196332.72520613723</v>
+        <v>885441.4066353055</v>
+      </c>
+      <c r="AR29" s="1">
+        <f>+AR23*20</f>
+        <v>2203261.5609587631</v>
+      </c>
+    </row>
+    <row r="30" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" s="2">
+        <v>1603.953</v>
+      </c>
+      <c r="Y30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AG30" s="1">
+        <f>PV(11%,9,0,-AG29)</f>
+        <v>115921.91368477407</v>
       </c>
       <c r="AM30" s="1">
-        <f>PV(11%,20,0,-AM29)</f>
-        <v>289923.90874245093</v>
+        <f>PV(11%,15,0,-AM29)</f>
+        <v>185061.1026909512</v>
+      </c>
+      <c r="AR30" s="1">
+        <f>PV(11%,20,0,-AR29)</f>
+        <v>273279.13974614098</v>
+      </c>
+    </row>
+    <row r="31" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="2">
+        <v>216.714</v>
+      </c>
+    </row>
+    <row r="32" spans="2:89" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M32" s="2">
+        <v>130.815</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M33" s="2">
+        <f>1540.889+421.868</f>
+        <v>1962.7569999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M34" s="2">
+        <v>761.89700000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="M35" s="2">
+        <f>SUM(M29:M34)</f>
+        <v>6343.0349999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="2">
+        <v>516.43799999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="2">
+        <v>510.947</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" s="2">
+        <v>45.747999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M40" s="2">
+        <v>3511.9650000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="2">
+        <v>284.017</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1473.92</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" s="2">
+        <f>SUM(M37:M42)</f>
+        <v>6343.0349999999999</v>
       </c>
     </row>
   </sheetData>
